--- a/docs/design-docs/04_画面設計書_異常報告.xlsx
+++ b/docs/design-docs/04_画面設計書_異常報告.xlsx
@@ -12,7 +12,464 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面設計書 — 異常報告一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>異常報告</t>
+  </si>
+  <si>
+    <t>画面ID</t>
+  </si>
+  <si>
+    <t>SCR-INC-LIST-001</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>異常報告一覧</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-INC-LIST-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INC-LIST-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>画面レイアウト</t>
+  </si>
+  <si>
+    <t>7条件複合検索（発生日×設備種別×異常種別×status×重大度×担当班×keyword）。検索条件保存/呼出。一覧checkbox付。一括status更新、CSV/PDF出力。</t>
+  </si>
+  <si>
+    <t>画面要素一覧</t>
+  </si>
+  <si>
+    <t>要素ID</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>入力値/選択肢</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>テスト難点タグ</t>
+  </si>
+  <si>
+    <t>inc-s-date-from/to</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>発生日from/to</t>
+  </si>
+  <si>
+    <t>YYYYMMDD</t>
+  </si>
+  <si>
+    <t>inc-s-type</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>設備種別</t>
+  </si>
+  <si>
+    <t>inc-s-inc-type</t>
+  </si>
+  <si>
+    <t>異常種別</t>
+  </si>
+  <si>
+    <t>絶縁不良/過熱/振動/油漏/ガス/コロナ/他</t>
+  </si>
+  <si>
+    <t>inc-s-status</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>全/未了/調査中/対応中/完了/再発防止/close</t>
+  </si>
+  <si>
+    <t>inc-s-severity</t>
+  </si>
+  <si>
+    <t>重大度</t>
+  </si>
+  <si>
+    <t>全/軽微/中/重大/緊急</t>
+  </si>
+  <si>
+    <t>inc-btn-save-cond</t>
+  </si>
+  <si>
+    <t>submit</t>
+  </si>
+  <si>
+    <t>検索条件保存</t>
+  </si>
+  <si>
+    <t>session保存→呼出</t>
+  </si>
+  <si>
+    <t>再現性</t>
+  </si>
+  <si>
+    <t>テーブル列定義</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>ソート</t>
+  </si>
+  <si>
+    <t>報告番号</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>INC-YYYYMMDD-NNN</t>
+  </si>
+  <si>
+    <t>発生日時</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>設備名</t>
+  </si>
+  <si>
+    <t>担当班</t>
+  </si>
+  <si>
+    <t>Struts1マッピング</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>Action Path</t>
+  </si>
+  <si>
+    <t>/inc/list</t>
+  </si>
+  <si>
+    <t>Action Class</t>
+  </si>
+  <si>
+    <t>IncidentListAction</t>
+  </si>
+  <si>
+    <t>Form Bean</t>
+  </si>
+  <si>
+    <t>IncidentSearchForm</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>inc.list.tiles</t>
+  </si>
+  <si>
+    <t>テスト難点詳細</t>
+  </si>
+  <si>
+    <t>7条件複合検索全組合わせ検証困難</t>
+  </si>
+  <si>
+    <t>検索条件保存→呼出再現性</t>
+  </si>
+  <si>
+    <t>画面設計書 — 異常報告登録</t>
+  </si>
+  <si>
+    <t>SCR-INC-CREATE-001</t>
+  </si>
+  <si>
+    <t>異常報告登録</t>
+  </si>
+  <si>
+    <t>PG-INC-CREATE-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INC-CREATE-001</t>
+  </si>
+  <si>
+    <t>3block構成：①発生情報(点検からdata引継) ②異常内容(種別/重大度/部位/詳細/添付max3) ③暫定処置。類似事例検索→同面下部結果表示。登録/一時保存。</t>
+  </si>
+  <si>
+    <t>inc-create-datetime</t>
+  </si>
+  <si>
+    <t>YYYYMMDD HH:MM</t>
+  </si>
+  <si>
+    <t>点検から引継</t>
+  </si>
+  <si>
+    <t>inc-create-type</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>inc-create-severity</t>
+  </si>
+  <si>
+    <t>軽微/中/重大/緊急</t>
+  </si>
+  <si>
+    <t>inc-create-file-{n}</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>添付{n}</t>
+  </si>
+  <si>
+    <t>max3枚</t>
+  </si>
+  <si>
+    <t>inc-btn-similar</t>
+  </si>
+  <si>
+    <t>類似事例検索</t>
+  </si>
+  <si>
+    <t>同面下部結果表示</t>
+  </si>
+  <si>
+    <t>DOM追加</t>
+  </si>
+  <si>
+    <t>/inc/create</t>
+  </si>
+  <si>
+    <t>IncidentCreateAction</t>
+  </si>
+  <si>
+    <t>IncidentForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>inc.list / inc.create</t>
+  </si>
+  <si>
+    <t>点検→異常報告data引継(hidden/session)</t>
+  </si>
+  <si>
+    <t>類似事例検索DOM動的追加</t>
+  </si>
+  <si>
+    <t>添付+validation同時</t>
+  </si>
+  <si>
+    <t>画面設計書 — 異常報告詳細</t>
+  </si>
+  <si>
+    <t>SCR-INC-DETAIL-001</t>
+  </si>
+  <si>
+    <t>異常報告詳細</t>
+  </si>
+  <si>
+    <t>PG-INC-DETAIL-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-INC-DETAIL-001</t>
+  </si>
+  <si>
+    <t>3block表示+経過記録timeline。多段階status遷移：未了→調査中→対応中→完了→close/再発防止。各遷移時条件付必須項目変化(推定原因/対応内容)。button表示/非表示切替。</t>
+  </si>
+  <si>
+    <t>inc-dtl-timeline</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>経過記録</t>
+  </si>
+  <si>
+    <t>登録→調査中→対応中→完了→再発防止</t>
+  </si>
+  <si>
+    <t>inc-dtl-btn-investigate</t>
+  </si>
+  <si>
+    <t>調査開始</t>
+  </si>
+  <si>
+    <t>未了時のみ表示</t>
+  </si>
+  <si>
+    <t>条件付button表示</t>
+  </si>
+  <si>
+    <t>inc-dtl-btn-counter</t>
+  </si>
+  <si>
+    <t>対応開始</t>
+  </si>
+  <si>
+    <t>調査中時のみ</t>
+  </si>
+  <si>
+    <t>推定原因必須</t>
+  </si>
+  <si>
+    <t>条件付必須</t>
+  </si>
+  <si>
+    <t>inc-dtl-cause</t>
+  </si>
+  <si>
+    <t>textarea</t>
+  </si>
+  <si>
+    <t>推定原因</t>
+  </si>
+  <si>
+    <t>調査→対応時必須</t>
+  </si>
+  <si>
+    <t>inc-dtl-btn-complete</t>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>対応中時のみ</t>
+  </si>
+  <si>
+    <t>対応内容必須</t>
+  </si>
+  <si>
+    <t>inc-dtl-btn-capa</t>
+  </si>
+  <si>
+    <t>再発防止策登録</t>
+  </si>
+  <si>
+    <t>完了時のみ</t>
+  </si>
+  <si>
+    <t>CAPAへ遷移</t>
+  </si>
+  <si>
+    <t>/inc/detail</t>
+  </si>
+  <si>
+    <t>IncidentDetailAction</t>
+  </si>
+  <si>
+    <t>IncidentForm</t>
+  </si>
+  <si>
+    <t>inc.detail / counter.capa</t>
+  </si>
+  <si>
+    <t>多段階遷移(5段階)全path網羅</t>
+  </si>
+  <si>
+    <t>各遷移時条件付必須項目</t>
+  </si>
+  <si>
+    <t>button表示/非表示状態別切替</t>
+  </si>
+  <si>
+    <t>timeline時系列sort</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
